--- a/public/vendor-docs/vendor-a-nextech-quote.xlsx
+++ b/public/vendor-docs/vendor-a-nextech-quote.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
   <si>
     <t>NexTech Systems Pvt. Ltd. — Commercial Quotation</t>
   </si>
@@ -162,6 +162,81 @@
   </si>
   <si>
     <t>NX-HUB7</t>
+  </si>
+  <si>
+    <t>24-Port Gigabit Switch, rack-mountable</t>
+  </si>
+  <si>
+    <t>NX-SW24</t>
+  </si>
+  <si>
+    <t>Wireless Access Point, Wi-Fi 6, PoE</t>
+  </si>
+  <si>
+    <t>NX-AP6</t>
+  </si>
+  <si>
+    <t>Adjustable Aluminium Laptop Stand</t>
+  </si>
+  <si>
+    <t>NX-STAND16</t>
+  </si>
+  <si>
+    <t>Wireless Presenter Clicker w/ Laser</t>
+  </si>
+  <si>
+    <t>NX-CLICK1</t>
+  </si>
+  <si>
+    <t>Conference Speakerphone, 6-mic, USB/BT</t>
+  </si>
+  <si>
+    <t>NX-SPK6</t>
+  </si>
+  <si>
+    <t>4K Conference Camera, auto-framing</t>
+  </si>
+  <si>
+    <t>NX-CAM4K</t>
+  </si>
+  <si>
+    <t>Desk-side UPS, 1kVA/600W</t>
+  </si>
+  <si>
+    <t>NX-UPS1K</t>
+  </si>
+  <si>
+    <t>6-Socket Surge Protector, 15A</t>
+  </si>
+  <si>
+    <t>NX-SURGE6</t>
+  </si>
+  <si>
+    <t>4-Bay NAS, diskless, GbE</t>
+  </si>
+  <si>
+    <t>NX-NAS4B</t>
+  </si>
+  <si>
+    <t>Ergonomic Vertical Mouse, wireless</t>
+  </si>
+  <si>
+    <t>NX-MSEV1</t>
+  </si>
+  <si>
+    <t>Endpoint Security License, 1yr/seat</t>
+  </si>
+  <si>
+    <t>NX-SEC1Y</t>
+  </si>
+  <si>
+    <t>centrally managed</t>
+  </si>
+  <si>
+    <t>Laptop Cable Lock, keyed</t>
+  </si>
+  <si>
+    <t>NX-LOCK1</t>
   </si>
   <si>
     <t>Payment terms: 30% advance, 70% on delivery. Freight: included within Bengaluru city limits.</t>
@@ -577,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -976,9 +1051,249 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
         <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23">
+        <v>9900</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>5400</v>
+      </c>
+      <c r="E24">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>990</v>
+      </c>
+      <c r="E25">
+        <v>175</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26">
+        <v>870</v>
+      </c>
+      <c r="E26">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27">
+        <v>14900</v>
+      </c>
+      <c r="E27">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28">
+        <v>11900</v>
+      </c>
+      <c r="E28">
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29">
+        <v>6000</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30">
+        <v>480</v>
+      </c>
+      <c r="E30">
+        <v>175</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31">
+        <v>25500</v>
+      </c>
+      <c r="E31">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32">
+        <v>1400</v>
+      </c>
+      <c r="E32">
+        <v>60</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>990</v>
+      </c>
+      <c r="E33">
+        <v>300</v>
+      </c>
+      <c r="F33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34">
+        <v>680</v>
+      </c>
+      <c r="E34">
+        <v>175</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -994,50 +1309,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
